--- a/manu_sourcedata/source_data_fig3.xlsx
+++ b/manu_sourcedata/source_data_fig3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yyj/Doc/1_dod_dec25/manu_sourcedata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F22F79DB-FEB9-5741-93AB-502A9179381E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7607E720-102E-944D-B6AD-DA6389B85FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="760" windowWidth="28040" windowHeight="17440" activeTab="5" xr2:uid="{2FBEDAAD-CA72-3F43-BF4C-EEE6D5E83CF9}"/>
+    <workbookView xWindow="38860" yWindow="60" windowWidth="28040" windowHeight="17440" activeTab="6" xr2:uid="{2FBEDAAD-CA72-3F43-BF4C-EEE6D5E83CF9}"/>
   </bookViews>
   <sheets>
     <sheet name="3b consensus" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="3c delta PAZWZN" sheetId="4" r:id="rId4"/>
     <sheet name="3c delta PBADJC" sheetId="5" r:id="rId5"/>
     <sheet name="3c delta PBBKFP" sheetId="6" r:id="rId6"/>
+    <sheet name="3c,d mannwhitney stats" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="28">
   <si>
     <t>source</t>
   </si>
@@ -92,6 +93,39 @@
   </si>
   <si>
     <t>delta</t>
+  </si>
+  <si>
+    <t>n_rebuilding</t>
+  </si>
+  <si>
+    <t>n_desertification</t>
+  </si>
+  <si>
+    <t>mean_delta_rebuilding</t>
+  </si>
+  <si>
+    <t>mean_delta_desertification</t>
+  </si>
+  <si>
+    <t>median_delta_rebuilding</t>
+  </si>
+  <si>
+    <t>median_delta_desertification</t>
+  </si>
+  <si>
+    <t>U_stat</t>
+  </si>
+  <si>
+    <t>p_one_sided_less</t>
+  </si>
+  <si>
+    <t>p_two_sided</t>
+  </si>
+  <si>
+    <t>min_possible_one_sided_p_with_n3_vs_n2</t>
+  </si>
+  <si>
+    <t>p_one_sided_less_fdr_bh</t>
   </si>
 </sst>
 </file>
@@ -4719,4 +4753,301 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F46106FF-9CCB-ED4E-8E38-1FC96FB8BA91}">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>-0.25886461823783202</v>
+      </c>
+      <c r="F2">
+        <v>2.68846487302062</v>
+      </c>
+      <c r="G2">
+        <v>0.343382809884893</v>
+      </c>
+      <c r="H2">
+        <v>2.68846487302062</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.1</v>
+      </c>
+      <c r="K2">
+        <v>0.2</v>
+      </c>
+      <c r="L2">
+        <v>0.1</v>
+      </c>
+      <c r="M2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>-0.69689832697231202</v>
+      </c>
+      <c r="F3">
+        <v>1.13398377717595</v>
+      </c>
+      <c r="G3">
+        <v>-0.35268289923915802</v>
+      </c>
+      <c r="H3">
+        <v>1.13398377717595</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.1</v>
+      </c>
+      <c r="K3">
+        <v>0.2</v>
+      </c>
+      <c r="L3">
+        <v>0.1</v>
+      </c>
+      <c r="M3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>-0.71978555102129305</v>
+      </c>
+      <c r="F4">
+        <v>1.29053826587695</v>
+      </c>
+      <c r="G4">
+        <v>-0.419356402375888</v>
+      </c>
+      <c r="H4">
+        <v>1.29053826587695</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.1</v>
+      </c>
+      <c r="K4">
+        <v>0.2</v>
+      </c>
+      <c r="L4">
+        <v>0.1</v>
+      </c>
+      <c r="M4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>-0.73066981484020699</v>
+      </c>
+      <c r="F5">
+        <v>1.2736302122862699</v>
+      </c>
+      <c r="G5">
+        <v>-0.245873184717851</v>
+      </c>
+      <c r="H5">
+        <v>1.2736302122862699</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.1</v>
+      </c>
+      <c r="K5">
+        <v>0.2</v>
+      </c>
+      <c r="L5">
+        <v>0.1</v>
+      </c>
+      <c r="M5">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>-0.58423169004282804</v>
+      </c>
+      <c r="F6">
+        <v>0.56543286867220399</v>
+      </c>
+      <c r="G6">
+        <v>-0.48661384259269702</v>
+      </c>
+      <c r="H6">
+        <v>0.56543286867220399</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.1</v>
+      </c>
+      <c r="K6">
+        <v>0.2</v>
+      </c>
+      <c r="L6">
+        <v>0.1</v>
+      </c>
+      <c r="M6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>-0.54858184366685103</v>
+      </c>
+      <c r="F7">
+        <v>0.57773701293754498</v>
+      </c>
+      <c r="G7">
+        <v>-0.45026148766458401</v>
+      </c>
+      <c r="H7">
+        <v>0.57773701293754498</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.1</v>
+      </c>
+      <c r="K7">
+        <v>0.2</v>
+      </c>
+      <c r="L7">
+        <v>0.1</v>
+      </c>
+      <c r="M7">
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>